--- a/entorno/mir-v2/plantillas/MPJ_DAE_2026_T1_MODELO.xlsx
+++ b/entorno/mir-v2/plantillas/MPJ_DAE_2026_T1_MODELO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="MPJ" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="DAE" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="INSTRUCCIONES" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="LISTAS" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MPJ" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DAE" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INSTRUCCIONES" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTAS" sheetId="4" state="hidden" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/entorno/mir-v2/plantillas/MPJ_DAE_2026_T1_MODELO.xlsx
+++ b/entorno/mir-v2/plantillas/MPJ_DAE_2026_T1_MODELO.xlsx
@@ -267,7 +267,7 @@
         <t>ID del Niño, niña o Adolescente
 Identificador alfanumérico nominal único provincial asignado al NyA para seguimiento resguardando su identidad. En caso de existir.
 Qué se espera: un número entero
-No es obligatorio.</t>
+Campo obligatorio.</t>
       </text>
     </comment>
     <comment ref="H3" authorId="0" shapeId="0">
@@ -623,7 +623,7 @@
       <text>
         <t>ID del Niño, niña o Adolescente
 Qué se espera: un número entero
-No es obligatorio.</t>
+Campo obligatorio.</t>
       </text>
     </comment>
     <comment ref="H3" authorId="0" shapeId="0">
@@ -1323,9 +1323,9 @@
           <t>Localidad</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>ID del Niño, niña o Adolescente</t>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>ID del Niño, niña o Adolescente *</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -3464,9 +3464,9 @@
           <t>Localidad</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>ID del Niño, niña o Adolescente</t>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>ID del Niño, niña o Adolescente *</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -6057,7 +6057,8 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Identificador alfanumérico nominal único provincial asignado al NyA para seguimiento resguardando su identidad. En caso de existir.</t>
+          <t>Identificador alfanumérico nominal único provincial asignado al NyA para seguimiento resguardando su identidad. En caso de existir.
+Campo obligatorio.</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6563,11 @@
           <t>ID del Niño, niña o Adolescente</t>
         </is>
       </c>
-      <c r="B54" s="11" t="n"/>
+      <c r="B54" s="11" t="inlineStr">
+        <is>
+          <t>Campo obligatorio.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">

--- a/entorno/mir-v2/plantillas/MPJ_DAE_2026_T1_MODELO.xlsx
+++ b/entorno/mir-v2/plantillas/MPJ_DAE_2026_T1_MODELO.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MPJ" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DAE" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INSTRUCCIONES" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTAS" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet name="MPJ" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="DAE" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Listas" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +22,7 @@
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="hh:mm"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,10 +41,6 @@
     </font>
     <font>
       <b val="1"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="12"/>
     </font>
   </fonts>
   <fills count="6">
@@ -102,7 +97,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -121,11 +116,6 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -205,354 +195,352 @@
 <file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>RUNAC</author>
+    <author>MIR</author>
   </authors>
   <commentList>
     <comment ref="A3" authorId="0" shapeId="0">
       <text>
         <t>Fecha del relevamiento
-Qué se espera: una fecha, con formato dd/mm/aaaa
-Campo obligatorio.</t>
+Obligatorio
+Qué va: Fecha, como día/mes/año.
+Aviso: No puede ser posterior a hoy.</t>
       </text>
     </comment>
     <comment ref="B3" authorId="0" shapeId="0">
       <text>
         <t>Provincia
-Identificar la provincia o jurisdicción correspondiente
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Provincias".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: 24 opciones, en el desplegable.
+Identificar la provincia o jurisdicción correspondiente</t>
       </text>
     </comment>
     <comment ref="C3" authorId="0" shapeId="0">
       <text>
         <t>Nombre del dispositivo
-Consignar el nombre completo del dispositivo (Establecimiento o Programa) en el cual se encuentran los jóvenes incluidos en el presente listado.
-Qué se espera: texto
-Máximo 120 caracteres.
-Campo obligatorio.</t>
+Obligatorio
+Qué va: Texto, hasta 120 caracteres.
+Aviso: Tiene que figurar en el DISP_PENAL del período.
+Consignar el nombre completo del dispositivo (Establecimiento o Programa) en el cual se encuentran los jóvenes incluidos en el presente listado.</t>
       </text>
     </comment>
     <comment ref="D3" authorId="0" shapeId="0">
       <text>
         <t>Tipo de dispositivo
-Seleccionar el tipo de dispositivo correspondiente de la lista desplegable: Medida Penal en Territorio, Establecimiento de Restricción de Libertad, Establecimiento de Privación de Libertad o Prisión Domiciliaria.
-Qué se espera: texto
-Máximo 42 caracteres.
-Elegir de la lista "Tipo de dispositivo".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Medida Penal en Territorio, Establecimiento de Restricción de Libertad, Establecimiento de Privación de Libertad, Prisión Domiciliara.
+Seleccionar el tipo de dispositivo correspondiente de la lista desplegable: Medida Penal en Territorio, Establecimiento de Restricción de Libertad, Establecimiento de Privación de Libertad o Prisión Domiciliaria.</t>
       </text>
     </comment>
     <comment ref="E3" authorId="0" shapeId="0">
       <text>
         <t>Dependencia institucional
-Indicar el organismo del cual depende el dispositivo con el siguiente orden: Ministerio, Secretaría, Dirección (según corresponda).
-Qué se espera: texto
-Máximo 255 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 255 caracteres.
+Indicar el organismo del cual depende el dispositivo con el siguiente orden: Ministerio, Secretaría, Dirección (según corresponda).</t>
       </text>
     </comment>
     <comment ref="F3" authorId="0" shapeId="0">
       <text>
         <t>Localidad
-Consignar localidad en la cual se encuentra ubicado el dispositivo.
-Qué se espera: texto
-Máximo 120 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 120 caracteres.
+Consignar localidad en la cual se encuentra ubicado el dispositivo.</t>
       </text>
     </comment>
     <comment ref="G3" authorId="0" shapeId="0">
       <text>
-        <t>ID del Niño, niña o Adolescente
-Identificador alfanumérico nominal único provincial asignado al NyA para seguimiento resguardando su identidad. En caso de existir.
-Qué se espera: un número entero
-Campo obligatorio.</t>
+        <t>ID del niño, niña o adolescente
+Obligatorio
+Qué va: Número entero.
+Aviso: Entre 1 y None.
+Entre 1 y 999999999.
+Tiene que figurar en el LEGAJO_NYA del período.
+Identificador alfanumérico nominal único provincial asignado al NyA para seguimiento resguardando su identidad. En caso de existir.</t>
       </text>
     </comment>
     <comment ref="H3" authorId="0" shapeId="0">
       <text>
         <t>Apellido/s
-Consignar el/los apellido/s del adolescente, tal como figura/n en su documentación.
-Qué se espera: texto
-Máximo 120 caracteres.
-Campo obligatorio.</t>
+Obligatorio
+Qué va: Texto, hasta 120 caracteres.
+Consignar el/los apellido/s del adolescente, tal como figura/n en su documentación.</t>
       </text>
     </comment>
     <comment ref="I3" authorId="0" shapeId="0">
       <text>
         <t>Nombre/s
-Consignar el/los nombre/s del adolescente, tal como figura/n en su documentación.
-Qué se espera: texto
-Máximo 120 caracteres.
-Campo obligatorio.</t>
+Obligatorio
+Qué va: Texto, hasta 120 caracteres.
+Consignar el/los nombre/s del adolescente, tal como figura/n en su documentación.</t>
       </text>
     </comment>
     <comment ref="J3" authorId="0" shapeId="0">
       <text>
         <t>Situación de documentación
-Consignar la situación de cada adolescente en relación a la documentación de acuerdo a las siguientes categorías que se encuentran en la lista desplegable: Posee N° DNI, No posee N° DNI, DNI en trámite, Posee N° documento extranjero o Sin datos. Cabe destacar que las opciones Posee N° DNI y No posee N° DNI hacen referencia al hecho de que se haya realizado o no el trámite para la obtención del Documento Nacional de Identidad. En este sentido, es importante mencionar que la indagación aquí realizada no permite identificar otro tipo de situaciones problemáticas vinculadas con la documentación, tales como la falta de renovación, o casos de extravío o deterioro de los mismos, entre otras.
-Qué se espera: texto
-Máximo 24 caracteres.
-Elegir de la lista "Situación de documentación".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Posee N° DNI, No posee N° DNI, DNI en trámite, Posee N° doc. Extranjero, Perdida de documentación, Sin inscripción, Sin datos.
+Consignar la situación de cada adolescente en relación a la documentación de acuerdo a las siguientes categorías que se encuentran en la lista desplegable: Posee N° DNI, No posee N° DNI, DNI en trámite, Posee N° documento extranjero o Sin datos. Cabe destacar que las opciones Posee N° DNI y No posee N° DNI hacen referencia al hecho de que se haya realizado o no el trámite para la obtención del Documento Nacional de Identidad. En este sentido, es importante mencionar que la indagación aquí realizada no permite identificar otro tipo de situaciones problemáticas vinculadas con la documentación, tales como la falta de renovación, o casos de extravío o deterioro de los mismos, entre otras.</t>
       </text>
     </comment>
     <comment ref="K3" authorId="0" shapeId="0">
       <text>
         <t>Nº DNI
-Informar el número de DNI del adolescente, sin puntos ni espacios.
-Qué se espera: texto
-Máximo 15 caracteres.
-No es obligatorio.</t>
+Obligatorio según otro dato
+Qué va: Texto, hasta 15 caracteres.
+Obligatorio si «Situación de documentación» es «Posee N° DNI», «Perdida de documentación».
+No se puede repetir en la hoja.
+No se puede repetir la combinación de «Nº DNI» + «Fecha de ingreso al dispositivo».
+Tiene que quedar vacío si «Situación de documentación» es «No posee N° DNI», «Sin inscripción», «DNI en trámite».
+Informar el número de DNI del adolescente, sin puntos ni espacios.</t>
       </text>
     </comment>
     <comment ref="L3" authorId="0" shapeId="0">
       <text>
         <t>Género
-Utilizar las categorías: Maculino, Femenino, Otros, Sin datos que se encuentran en la lista desplegable.
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Género".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Masculino, Femenino, Otros, Sin datos.
+Utilizar las categorías: Maculino, Femenino, Otros, Sin datos que se encuentran en la lista desplegable.</t>
       </text>
     </comment>
     <comment ref="M3" authorId="0" shapeId="0">
       <text>
         <t>País de nacimiento
-Indicar el país de origen de cada adolescente según el desplegable incluido.
-Qué se espera: texto
-Máximo 44 caracteres.
-Elegir de la lista "País de nacimiento".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: 246 opciones, en el desplegable.
+Indicar el país de origen de cada adolescente según el desplegable incluido.</t>
       </text>
     </comment>
     <comment ref="N3" authorId="0" shapeId="0">
       <text>
         <t>Fecha de nacimiento
-Especificar la fecha de nacimiento del adolescente utilizando el siguiente formato: DD/MM/AAAA. Por ejemplo: 01/03/2001.
-Qué se espera: una fecha, con formato dd/mm/aaaa
-Campo obligatorio.</t>
+Obligatorio
+Qué va: Fecha, como día/mes/año.
+Aviso: No puede ser posterior a hoy.
+Especificar la fecha de nacimiento del adolescente utilizando el siguiente formato: DD/MM/AAAA. Por ejemplo: 01/03/2001.</t>
       </text>
     </comment>
     <comment ref="O3" authorId="0" shapeId="0">
       <text>
         <t>Edad
-Consignar la edad del adolescente a la fecha del presente relevamiento.
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.
+Aviso: Entre 0 y 17.
+Entre 0 y 120.
+Consignar la edad del adolescente a la fecha del presente relevamiento.</t>
       </text>
     </comment>
     <comment ref="P3" authorId="0" shapeId="0">
       <text>
         <t>¿Asiste a institución educativa?
-Seleccionar de la lista desplegable.
-Qué se espera: texto
-Máximo 22 caracteres.
-Elegir de la lista "¿Asiste a institución educativa?".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí asiste, No asiste pero asistió, Nunca asistió, Sin datos.
+Seleccionar de la lista desplegable.</t>
       </text>
     </comment>
     <comment ref="Q3" authorId="0" shapeId="0">
       <text>
         <t>Máximo nivel educativo alcanzado
-Seleccionar en el menú desplegable, el nivel educativo alcanzado a la fecha del relevamiento.
-Qué se espera: texto
-Máximo 24 caracteres.
-Elegir de la lista "Máximo nivel educativo alcanzado".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: 12 opciones, en el desplegable.
+Seleccionar en el menú desplegable, el nivel educativo alcanzado a la fecha del relevamiento.</t>
       </text>
     </comment>
     <comment ref="R3" authorId="0" shapeId="0">
       <text>
         <t>Enfermedad crónica
-Indicar si el adolescente presenta alguna enfermedad crónica.
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "¿Presenta alguna discapacidad?".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: No, Sin datos, Sí.
+Indicar si el adolescente presenta alguna enfermedad crónica.</t>
       </text>
     </comment>
     <comment ref="S3" authorId="0" shapeId="0">
       <text>
         <t>Consumo problemático de sustancias
-Indicar si el adolescente presenta consumo problemático de sustancias.
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "¿Presenta alguna discapacidad?".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: No, Sin datos, Sí.
+Indicar si el adolescente presenta consumo problemático de sustancias.</t>
       </text>
     </comment>
     <comment ref="T3" authorId="0" shapeId="0">
       <text>
         <t>¿Presenta alguna discapacidad?
-Indicar si el adolescente presenta alguna discapacidad. En caso de responder positivamente, en la columna siguiente deberá especificar el tipo de discapacidad.
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "¿Presenta alguna discapacidad?".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: No, Sin datos, Sí.
+Indicar si el adolescente presenta alguna discapacidad. En caso de responder positivamente, en la columna siguiente deberá especificar el tipo de discapacidad.</t>
       </text>
     </comment>
     <comment ref="U3" authorId="0" shapeId="0">
       <text>
         <t>Tipo de discapacidad
-Seleccionar el tipo de discapacidad según las opciones proporcionadas en el desplegable: visual, auditiva, mental, visceral, motora, otros (especificar en observaciones), sin datos.
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Tipo de discapacidad".
-No es obligatorio.</t>
+Obligatorio según otro dato
+Qué va: Una opción de la lista.
+Valores: Visual, Auditiva, Mental, Motora, Visceral, Otros, Sin datos.
+Obligatorio si «¿Presenta alguna discapacidad?» es «Si».
+Seleccionar el tipo de discapacidad según las opciones proporcionadas en el desplegable: visual, auditiva, mental, visceral, motora, otros (especificar en observaciones), sin datos.</t>
       </text>
     </comment>
     <comment ref="V3" authorId="0" shapeId="0">
       <text>
         <t>¿Posee CUD?
-Responder según opciones del desplegable: Sí, No, En trámite, Sin datos. El Certificado Único de Discapacidad (CUD) es un documento que certifica la discapacidad de la persona y le permite acceder a derechos y prestaciones que brinda el Estado. El CUD es un documento público válido en todo el país que permite ejercer los derechos y acceder a las prestaciones previstas en las leyes nacionales 22.431 y 24.901.
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "¿Posee CUD?".
-No es obligatorio.</t>
+Obligatorio según otro dato
+Qué va: Una opción de la lista.
+Valores: Sí, No, En trámite, Sin datos.
+Obligatorio si «¿Presenta alguna discapacidad?» es «Si».
+Responder según opciones del desplegable: Sí, No, En trámite, Sin datos. El Certificado Único de Discapacidad (CUD) es un documento que certifica la discapacidad de la persona y le permite acceder a derechos y prestaciones que brinda el Estado. El CUD es un documento público válido en todo el país que permite ejercer los derechos y acceder a las prestaciones previstas en las leyes nacionales 22.431 y 24.901.</t>
       </text>
     </comment>
     <comment ref="W3" authorId="0" shapeId="0">
       <text>
         <t>Cobertura salud
-Responder según opciones del desplegable: PAMI, IOMA, Obra social provincial, Obra social privada, Prepaga, Sin cobertura, Sin datos
-Qué se espera: texto
-Máximo 22 caracteres.
-Elegir de la lista "Cobertura salud".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: PAMI, IOMA, Obra social provincial, Obra social privada, Prepaga, Sin cobertura, Sin datos.
+Responder según opciones del desplegable: PAMI, IOMA, Obra social provincial, Obra social privada, Prepaga, Sin cobertura, Sin datos</t>
       </text>
     </comment>
     <comment ref="X3" authorId="0" shapeId="0">
       <text>
         <t>¿Se identifica con algún pueblo originario?
-Consignar si el joven pertenece a un pueblo originario, utilizando las categorías Sí, No o Sin datos del desplegable. En caso de que la respuesta sea Sí , deberá especificarse en la columna siguiente el pueblo originario con el cual el adolescente se identifica, en caso de que la respuesta sea No, consignar en la columna siguiente No corresponde.
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "¿Presenta alguna discapacidad?".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: No, Sin datos, Sí.
+Consignar si el joven pertenece a un pueblo originario, utilizando las categorías Sí, No o Sin datos del desplegable. En caso de que la respuesta sea Sí , deberá especificarse en la columna siguiente el pueblo originario con el cual el adolescente se identifica, en caso de que la respuesta sea No, consignar en la columna siguiente No corresponde.</t>
       </text>
     </comment>
     <comment ref="Y3" authorId="0" shapeId="0">
       <text>
         <t>Pueblo originario (especificar)
-Pregunta abierta.
-Qué se espera: texto
-No es obligatorio.</t>
+Obligatorio según otro dato
+Qué va: Texto.
+Obligatorio si «¿Se identifica con algún pueblo originario?» es «Sí».
+Pregunta abierta.</t>
       </text>
     </comment>
     <comment ref="Z3" authorId="0" shapeId="0">
       <text>
         <t>Asignación Universal por Hijo
-Indicar si el joven percibe o no la Asignación Universal por Hijo de acuerdo a los ítems de respuesta desplegables. Debe tenerse en cuenta que aunque el/la adolescente sea titular de la percepción del beneficio no implica que sea la persona que recibe el dinero de la asignación. La percepción refiere sólo a la titularidad.
-Qué se espera: texto
-Máximo 27 caracteres.
-Elegir de la lista "Asignación Universal por Hijo".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Percibe AUH, No percibe pero corresponde, No percibe y no corresponde, Sin datos.
+Indicar si el joven percibe o no la Asignación Universal por Hijo de acuerdo a los ítems de respuesta desplegables. Debe tenerse en cuenta que aunque el/la adolescente sea titular de la percepción del beneficio no implica que sea la persona que recibe el dinero de la asignación. La percepción refiere sólo a la titularidad.</t>
       </text>
     </comment>
     <comment ref="AA3" authorId="0" shapeId="0">
       <text>
         <t>¿Tiene hijos/as?
-Completarse por Sí, No o Sin datos. Es indistinto si los/as hijos/as se encuentran en el dispositivo junto a sus progenitores/as.
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "¿Presenta alguna discapacidad?".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: No, Sin datos, Sí.
+Completarse por Sí, No o Sin datos. Es indistinto si los/as hijos/as se encuentran en el dispositivo junto a sus progenitores/as.</t>
       </text>
     </comment>
     <comment ref="AB3" authorId="0" shapeId="0">
       <text>
         <t>Descripción causa penal/contravención
-Identificar la causa penal o contravención por la cual el/la adolescente se encuentra en el dispositivo. En caso de que exista más de una causa, por favor consignar todas.
-Qué se espera: texto
-No es obligatorio.</t>
+Opcional
+Qué va: Texto.
+Identificar la causa penal o contravención por la cual el/la adolescente se encuentra en el dispositivo. En caso de que exista más de una causa, por favor consignar todas.</t>
       </text>
     </comment>
     <comment ref="AC3" authorId="0" shapeId="0">
       <text>
         <t>Fecha de ingreso al dispositivo
-Especificar el día de ingreso del adolescente al dispositivo utilizando el siguiente formato DD/MD/AAAA. Ej.: 01/02/2021
-Qué se espera: una fecha, con formato dd/mm/aaaa
-No es obligatorio.</t>
+Opcional
+Qué va: Fecha, como día/mes/año.
+Aviso: No puede ser posterior a hoy.
+Especificar el día de ingreso del adolescente al dispositivo utilizando el siguiente formato DD/MD/AAAA. Ej.: 01/02/2021</t>
       </text>
     </comment>
     <comment ref="AD3" authorId="0" shapeId="0">
       <text>
         <t>Procedencia inmediata
-Consignar la procedencia inmediatamente anterior al ingreso al dispositivo, de acuerdo con las siguientes opciones: Policía provincial, Gendarmería, Prefectura, Infantería, CAD, Comisaría, Juzgado (sin intervención de otro dispositivo penal juvenil), Establecimiento de privación de libertad, Establecimiento de restricción de libertad, Medida penal en territorio, Defensoría de menores, Otros o Sin datos.
-Qué se espera: texto
-Máximo 42 caracteres.
-Elegir de la lista "Procedencia inmediata".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: 13 opciones, en el desplegable.
+Consignar la procedencia inmediatamente anterior al ingreso al dispositivo, de acuerdo con las siguientes opciones: Policía provincial, Gendarmería, Prefectura, Infantería, CAD, Comisaría, Juzgado (sin intervención de otro dispositivo penal juvenil), Establecimiento de privación de libertad, Establecimiento de restricción de libertad, Medida penal en territorio, Defensoría de menores, Otros o Sin datos.</t>
       </text>
     </comment>
     <comment ref="AE3" authorId="0" shapeId="0">
       <text>
         <t>Especificar procedencia
-En caso de ser derivado por una comisaría, especificar el número de comisaría. Si se trata de un CAD, Establecimiento de privación de libertad, Establecimiento de restricción de libertad, Medida penal en territorio, indicar el nombre del dispositivo y localización geográfica.
-Qué se espera: texto
-No es obligatorio.</t>
+Obligatorio según otro dato
+Qué va: Texto.
+Obligatorio si «Procedencia inmediata» es «Otros».
+En caso de ser derivado por una comisaría, especificar el número de comisaría. Si se trata de un CAD, Establecimiento de privación de libertad, Establecimiento de restricción de libertad, Medida penal en territorio, indicar el nombre del dispositivo y localización geográfica.</t>
       </text>
     </comment>
     <comment ref="AF3" authorId="0" shapeId="0">
       <text>
         <t>Dependencia judicial
-Consignar la dependencia Judicial.
-Qué se espera: texto
-Máximo 255 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 255 caracteres.
+Consignar la dependencia Judicial.</t>
       </text>
     </comment>
     <comment ref="AG3" authorId="0" shapeId="0">
       <text>
         <t>Situación procesal
-Consignar la situación procesal de el/la adolescente utilizando las categorías del desplegable: Investigación penal, Elevación a juicio, Declaración de responsabilidad, Ejecución penal, Sentencia a revisión, Otros, Sin datos. En caso de encontrarse en etapa de Ejecución Penal, especificar el monto de la pena en la columna siguiente.
-Qué se espera: texto
-Máximo 30 caracteres.
-Elegir de la lista "Situación procesal".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Investigación penal, Elevación a juicio, Declaración de responsabilidad, Ejecución penal, Sentencia a revisión, Otros, Sin datos.
+Consignar la situación procesal de el/la adolescente utilizando las categorías del desplegable: Investigación penal, Elevación a juicio, Declaración de responsabilidad, Ejecución penal, Sentencia a revisión, Otros, Sin datos. En caso de encontrarse en etapa de Ejecución Penal, especificar el monto de la pena en la columna siguiente.</t>
       </text>
     </comment>
     <comment ref="AH3" authorId="0" shapeId="0">
       <text>
         <t>Monto de la pena
-Pregunta abierta. Entrada numérica según cada caso individual.
-Qué se espera: un número, puede tener decimales
-No es obligatorio.</t>
+Opcional
+Qué va: Número con decimales.
+Aviso: Entre 0 y None.
+Entre 0 y 100000.
+Pregunta abierta. Entrada numérica según cada caso individual.</t>
       </text>
     </comment>
     <comment ref="AI3" authorId="0" shapeId="0">
       <text>
         <t>Fecha de egreso del dispositivo
-Especificar el día de egreso del adolescente al dispositivo utilizando el siguiente formato DD/MD/AAAA. Ej.: 01/02/2021
-Qué se espera: una fecha, con formato dd/mm/aaaa
-No es obligatorio.</t>
+Opcional
+Qué va: Fecha, como día/mes/año.
+Aviso: No puede ser posterior a hoy.
+"Fecha de egreso del dispositivo" no puede ser anterior a "Fecha de ingreso al dispositivo" ()
+Especificar el día de egreso del adolescente al dispositivo utilizando el siguiente formato DD/MD/AAAA. Ej.: 01/02/2021</t>
       </text>
     </comment>
     <comment ref="AJ3" authorId="0" shapeId="0">
       <text>
         <t>Destino al egreso
-Responder utilizando las categorías del desplegable.
-Qué se espera: texto
-Máximo 35 caracteres.
-Elegir de la lista "Destino al egreso".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: 10 opciones, en el desplegable.
+Responder utilizando las categorías del desplegable.</t>
       </text>
     </comment>
     <comment ref="AK3" authorId="0" shapeId="0">
       <text>
         <t>Especificar destino al egreso
-En caso de que en la columna anterior se haya elegido egreso a un dispositivo penal, consignar el nombre del mismo.
-Qué se espera: texto
-No es obligatorio.</t>
+Obligatorio según otro dato
+Qué va: Texto.
+Obligatorio si «Destino al egreso» es «Otros».
+Aviso: No puede ser posterior a hoy.
+"Especificar destino al egreso" no puede ser anterior a "Fecha de ingreso al dispositivo" ()
+En caso de que en la columna anterior se haya elegido egreso a un dispositivo penal, consignar el nombre del mismo.</t>
       </text>
     </comment>
     <comment ref="AL3" authorId="0" shapeId="0">
       <text>
         <t>Observaciones
-Qué se espera: texto
-No es obligatorio.</t>
+Opcional
+Qué va: Texto.</t>
       </text>
     </comment>
   </commentList>
@@ -562,374 +550,368 @@
 <file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>RUNAC</author>
+    <author>MIR</author>
   </authors>
   <commentList>
     <comment ref="A3" authorId="0" shapeId="0">
       <text>
         <t>Fecha del relevamiento
-Qué se espera: una fecha, con formato dd/mm/aaaa
-Campo obligatorio.</t>
+Obligatorio
+Qué va: Fecha, como día/mes/año.
+Aviso: No puede ser posterior a hoy.</t>
       </text>
     </comment>
     <comment ref="B3" authorId="0" shapeId="0">
       <text>
         <t>Provincia
-Identificar la provincia o jurisdicción correspondiente
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Provincias".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: 24 opciones, en el desplegable.
+Identificar la provincia o jurisdicción correspondiente</t>
       </text>
     </comment>
     <comment ref="C3" authorId="0" shapeId="0">
       <text>
         <t>Nombre del dispositivo
-Consignar el nombre completo del dispositivo (Establecimiento o Programa) en el cual se encuentran los jóvenes incluidos en el presente listado.
-Qué se espera: texto
-Máximo 120 caracteres.
-Campo obligatorio.</t>
+Obligatorio
+Qué va: Texto, hasta 120 caracteres.
+Aviso: Tiene que figurar en el DISP_PENAL del período.
+Consignar el nombre completo del dispositivo (Establecimiento o Programa) en el cual se encuentran los jóvenes incluidos en el presente listado.</t>
       </text>
     </comment>
     <comment ref="D3" authorId="0" shapeId="0">
       <text>
         <t>Tipo de dispositivo
-Seleccionar el tipo de dispositivo correspondiente de la lista desplegable: Medida Penal en Territorio, Establecimiento de Restricción de Libertad, Establecimiento de Privación de Libertad o Prisión Domiciliaria.
-Qué se espera: texto
-Máximo 31 caracteres.
-Elegir de la lista "Tipo de dispositivo".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Centro de Admisión y Derivación, Guardia en Comisaría.
+Seleccionar el tipo de dispositivo correspondiente de la lista desplegable: Medida Penal en Territorio, Establecimiento de Restricción de Libertad, Establecimiento de Privación de Libertad o Prisión Domiciliaria.</t>
       </text>
     </comment>
     <comment ref="E3" authorId="0" shapeId="0">
       <text>
         <t>Dependencia institucional
-Indicar el organismo del cual depende el dispositivo con el siguiente orden: Ministerio, Secretaría, Dirección (según corresponda).
-Qué se espera: texto
-Máximo 255 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 255 caracteres.
+Indicar el organismo del cual depende el dispositivo con el siguiente orden: Ministerio, Secretaría, Dirección (según corresponda).</t>
       </text>
     </comment>
     <comment ref="F3" authorId="0" shapeId="0">
       <text>
         <t>Localidad
-Consignar localidad en la cual se encuentra ubicado el dispositivo.
-Qué se espera: texto
-Máximo 120 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 120 caracteres.
+Consignar localidad en la cual se encuentra ubicado el dispositivo.</t>
       </text>
     </comment>
     <comment ref="G3" authorId="0" shapeId="0">
       <text>
-        <t>ID del Niño, niña o Adolescente
-Qué se espera: un número entero
-Campo obligatorio.</t>
+        <t>ID del niño, niña o adolescente
+Obligatorio
+Qué va: Número entero.
+Tiene que figurar en el LEGAJO_NYA del período.</t>
       </text>
     </comment>
     <comment ref="H3" authorId="0" shapeId="0">
       <text>
         <t>Apellido/s
-Qué se espera: texto
-Máximo 120 caracteres.
-Campo obligatorio.</t>
+Obligatorio
+Qué va: Texto, hasta 120 caracteres.</t>
       </text>
     </comment>
     <comment ref="I3" authorId="0" shapeId="0">
       <text>
         <t>Nombre/s
-Qué se espera: texto
-Máximo 120 caracteres.
-Campo obligatorio.</t>
+Obligatorio
+Qué va: Texto, hasta 120 caracteres.</t>
       </text>
     </comment>
     <comment ref="J3" authorId="0" shapeId="0">
       <text>
         <t>Situación de documentación
-Qué se espera: texto
-Máximo 24 caracteres.
-Elegir de la lista "Situación de documentación".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Posee N° DNI, No posee N° DNI, DNI en trámite, Posee N° doc. Extranjero, Perdida de documentación, Sin inscripción, Sin datos.</t>
       </text>
     </comment>
     <comment ref="K3" authorId="0" shapeId="0">
       <text>
         <t>Nº DNI
-Qué se espera: texto
-Máximo 15 caracteres.
-No es obligatorio.</t>
+Obligatorio según otro dato
+Qué va: Texto, hasta 15 caracteres.
+Obligatorio si «Situación de documentación» es «Posee N° DNI», «Perdida de documentación».
+No se puede repetir en la hoja.
+No se puede repetir la combinación de «Nº DNI» + «Fecha de ingreso al dispositivo».
+Tiene que quedar vacío si «Situación de documentación» es «No posee N° DNI», «Sin inscripción», «DNI en trámite».</t>
       </text>
     </comment>
     <comment ref="L3" authorId="0" shapeId="0">
       <text>
         <t>Género
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Género".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Masculino, Femenino, Otros, Sin datos.</t>
       </text>
     </comment>
     <comment ref="M3" authorId="0" shapeId="0">
       <text>
         <t>País de nacimiento
-Qué se espera: texto
-Máximo 44 caracteres.
-Elegir de la lista "País de nacimiento".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: 246 opciones, en el desplegable.</t>
       </text>
     </comment>
     <comment ref="N3" authorId="0" shapeId="0">
       <text>
         <t>Fecha de nacimiento
-Qué se espera: una fecha, con formato dd/mm/aaaa
-Campo obligatorio.</t>
+Obligatorio
+Qué va: Fecha, como día/mes/año.
+Aviso: No puede ser posterior a hoy.</t>
       </text>
     </comment>
     <comment ref="O3" authorId="0" shapeId="0">
       <text>
         <t>Edad
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.
+Aviso: Entre 0 y 17.
+Entre 0 y 120.</t>
       </text>
     </comment>
     <comment ref="P3" authorId="0" shapeId="0">
       <text>
         <t>¿Asiste a institución educativa?
-Qué se espera: texto
-Máximo 22 caracteres.
-Elegir de la lista "¿Asiste a institución educativa?".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí asiste, No asiste pero asistió, Nunca asistió, Sin datos.</t>
       </text>
     </comment>
     <comment ref="Q3" authorId="0" shapeId="0">
       <text>
         <t>Máximo nivel educativo alcanzado
-Qué se espera: texto
-Máximo 24 caracteres.
-Elegir de la lista "Máximo nivel educativo alcanzado".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: 12 opciones, en el desplegable.</t>
       </text>
     </comment>
     <comment ref="R3" authorId="0" shapeId="0">
       <text>
         <t>Enfermedad crónica
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "¿Presenta alguna discapacidad?".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: No, Sin datos, Sí.</t>
       </text>
     </comment>
     <comment ref="S3" authorId="0" shapeId="0">
       <text>
         <t>Consumo problemático de sustancias
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "¿Presenta alguna discapacidad?".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: No, Sin datos, Sí.</t>
       </text>
     </comment>
     <comment ref="T3" authorId="0" shapeId="0">
       <text>
         <t>¿Presenta alguna discapacidad?
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "¿Presenta alguna discapacidad?".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: No, Sin datos, Sí.</t>
       </text>
     </comment>
     <comment ref="U3" authorId="0" shapeId="0">
       <text>
         <t>Tipo de discapacidad
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Tipo de discapacidad".
-No es obligatorio.</t>
+Obligatorio según otro dato
+Qué va: Una opción de la lista.
+Valores: Visual, Auditiva, Mental, Motora, Visceral, Otros, Sin datos.
+Obligatorio si «¿Presenta alguna discapacidad?» es «Si».</t>
       </text>
     </comment>
     <comment ref="V3" authorId="0" shapeId="0">
       <text>
         <t>¿Posee CUD?
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "¿Posee CUD?".
-No es obligatorio.</t>
+Obligatorio según otro dato
+Qué va: Una opción de la lista.
+Valores: Sí, No, En trámite, Sin datos.
+Obligatorio si «¿Presenta alguna discapacidad?» es «Si».</t>
       </text>
     </comment>
     <comment ref="W3" authorId="0" shapeId="0">
       <text>
         <t>Cobertura salud
-Qué se espera: texto
-Máximo 22 caracteres.
-Elegir de la lista "Cobertura salud".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: PAMI, IOMA, Obra social provincial, Obra social privada, Prepaga, Sin cobertura, Sin datos.</t>
       </text>
     </comment>
     <comment ref="X3" authorId="0" shapeId="0">
       <text>
         <t>¿Se identifica con algún pueblo originario?
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "¿Presenta alguna discapacidad?".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: No, Sin datos, Sí.</t>
       </text>
     </comment>
     <comment ref="Y3" authorId="0" shapeId="0">
       <text>
         <t>Pueblo originario (especificar)
-Qué se espera: texto
-No es obligatorio.</t>
+Obligatorio según otro dato
+Qué va: Texto.
+Obligatorio si «¿Se identifica con algún pueblo originario?» es «Sí».</t>
       </text>
     </comment>
     <comment ref="Z3" authorId="0" shapeId="0">
       <text>
         <t>¿Tiene hijos/as?
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "¿Presenta alguna discapacidad?".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: No, Sin datos, Sí.</t>
       </text>
     </comment>
     <comment ref="AA3" authorId="0" shapeId="0">
       <text>
         <t>Motivo de la aprehensión
-Qué se espera: texto
-Máximo 28 caracteres.
-Elegir de la lista "Motivo de la aprehensión".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Contravención, Presunto delito, Presunto delito/flagrancia, Averiguación de antecedentes, Protección de derechos, Vulneración de derechos, Sin datos.</t>
       </text>
     </comment>
     <comment ref="AB3" authorId="0" shapeId="0">
       <text>
         <t>Descripción causa/contravención
-Identificar la causa penal o contravención por la cual el/la adolescente se encuentra en el dispositivo. En caso de que exista más de una causa, por favor consignar todas.
-Qué se espera: texto
-No es obligatorio.</t>
+Opcional
+Qué va: Texto.
+Identificar la causa penal o contravención por la cual el/la adolescente se encuentra en el dispositivo. En caso de que exista más de una causa, por favor consignar todas.</t>
       </text>
     </comment>
     <comment ref="AC3" authorId="0" shapeId="0">
       <text>
         <t>Fecha de ingreso al dispositivo
-Qué se espera: una fecha, con formato dd/mm/aaaa
-No es obligatorio.</t>
+Opcional
+Qué va: Fecha, como día/mes/año.
+Aviso: No puede ser posterior a hoy.</t>
       </text>
     </comment>
     <comment ref="AD3" authorId="0" shapeId="0">
       <text>
         <t>Hora de ingreso al dispositivo
-Consignar la hora de ingreso al establecimiento utilizando el siguiente formato HH:MM, en formato 24 hs. Ej.: 22:30. Recuerde utilizar los dos puntos para separar hora de minutos.
-Qué se espera: una hora, con formato hh:mm
-No es obligatorio.</t>
+Opcional
+Qué va: Hora, como hh:mm.
+Aviso: No puede ser posterior a hoy.
+Consignar la hora de ingreso al establecimiento utilizando el siguiente formato HH:MM, en formato 24 hs. Ej.: 22:30. Recuerde utilizar los dos puntos para separar hora de minutos.</t>
       </text>
     </comment>
     <comment ref="AE3" authorId="0" shapeId="0">
       <text>
         <t>Fuerza de seguridad
-Identificar la fuerza de seguridad que ha efectuado la aprehensión de acuerdo con las opciones que aparecen en el desplegable: Policía Municipal, Policía Provincial, Policía Federal, Gendarmería, Prefectura, Infantería, Otros, Sin datos.
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Fuerza de seguridad".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Policía Provincial, Policía Municipal, Policía Federal, Gendarmería, Prefectura, Infantería, Otros, Sin datos.
+Identificar la fuerza de seguridad que ha efectuado la aprehensión de acuerdo con las opciones que aparecen en el desplegable: Policía Municipal, Policía Provincial, Policía Federal, Gendarmería, Prefectura, Infantería, Otros, Sin datos.</t>
       </text>
     </comment>
     <comment ref="AF3" authorId="0" shapeId="0">
       <text>
         <t>N° comisaría o dependencia
-Detallar la dependencia a la que pertenece la fuerza que ha efectuado la aprehensión, de acuerdo con las siguientes opciones: Comisaría N° XX, Alcaldía N° XX, u otro/s.
-Qué se espera: texto
-Máximo 255 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 255 caracteres.
+Detallar la dependencia a la que pertenece la fuerza que ha efectuado la aprehensión, de acuerdo con las siguientes opciones: Comisaría N° XX, Alcaldía N° XX, u otro/s.</t>
       </text>
     </comment>
     <comment ref="AG3" authorId="0" shapeId="0">
       <text>
         <t>Departamento de la dependencia
-Especificar el departamento en el cual se ubica la dependencia policial de procedencia que efectuó la aprehensión.
-Qué se espera: texto
-Máximo 255 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 255 caracteres.
+Especificar el departamento en el cual se ubica la dependencia policial de procedencia que efectuó la aprehensión.</t>
       </text>
     </comment>
     <comment ref="AH3" authorId="0" shapeId="0">
       <text>
         <t>¿Pasó por comisaría previo ingreso?
-Consignar si el adolescente pasó o no por una comisaría (tanto por trámites policiales y/o permanencia) previamente a su ingreso al establecimiento especializado de aprehensión según desplegable.
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "¿Presenta alguna discapacidad?".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: No, Sin datos, Sí.
+Consignar si el adolescente pasó o no por una comisaría (tanto por trámites policiales y/o permanencia) previamente a su ingreso al establecimiento especializado de aprehensión según desplegable.</t>
       </text>
     </comment>
     <comment ref="AI3" authorId="0" shapeId="0">
       <text>
         <t>Tiempo en comisaría
-Especificar el tiempo de permanencia en la comisaría, de acuerdo con las opciones que ofrece el listado desplegable: Hasta 12 hs., Entre 12 y 24 hs., etc. Seleccionar del listado desplegable. En caso que el NNyA no haya pasado previamente por una dependencia policial, seleccionar No corresponde.
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Tiempo en comisaría".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: 12 opciones, en el desplegable.
+Especificar el tiempo de permanencia en la comisaría, de acuerdo con las opciones que ofrece el listado desplegable: Hasta 12 hs., Entre 12 y 24 hs., etc. Seleccionar del listado desplegable. En caso que el NNyA no haya pasado previamente por una dependencia policial, seleccionar No corresponde.</t>
       </text>
     </comment>
     <comment ref="AJ3" authorId="0" shapeId="0">
       <text>
         <t>Fecha de egreso del dispositivo
-Qué se espera: una fecha, con formato dd/mm/aaaa
-No es obligatorio.</t>
+Opcional
+Qué va: Fecha, como día/mes/año.
+Aviso: No puede ser posterior a hoy.
+"Fecha de egreso del dispositivo" no puede ser anterior a "Fecha de ingreso al dispositivo" ()</t>
       </text>
     </comment>
     <comment ref="AK3" authorId="0" shapeId="0">
       <text>
         <t>Hora de egreso del dispositivo
-Consignar la hora de egreso del dispositivo utilizando el siguiente formato HH:MM, en formato 24 hs. Ej.: 22:30. Recuerde utilizar los dos puntos para separar hora de minutos.
-Qué se espera: una hora, con formato hh:mm
-No es obligatorio.</t>
+Opcional
+Qué va: Hora, como hh:mm.
+Aviso: No puede ser posterior a hoy.
+"Hora de egreso del dispositivo" no puede ser anterior a "Fecha de ingreso al dispositivo" ()
+Consignar la hora de egreso del dispositivo utilizando el siguiente formato HH:MM, en formato 24 hs. Ej.: 22:30. Recuerde utilizar los dos puntos para separar hora de minutos.</t>
       </text>
     </comment>
     <comment ref="AL3" authorId="0" shapeId="0">
       <text>
         <t>Destino al egreso
-Qué se espera: texto
-Máximo 35 caracteres.
-Elegir de la lista "Destino al egreso".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: 10 opciones, en el desplegable.</t>
       </text>
     </comment>
     <comment ref="AM3" authorId="0" shapeId="0">
       <text>
         <t>Especificar destino al egreso
-Qué se espera: texto
-No es obligatorio.</t>
+Obligatorio según otro dato
+Qué va: Texto.
+Obligatorio si «Destino al egreso» es «Otros».
+Aviso: No puede ser posterior a hoy.
+"Especificar destino al egreso" no puede ser anterior a "Fecha de ingreso al dispositivo" ()</t>
       </text>
     </comment>
     <comment ref="AN3" authorId="0" shapeId="0">
       <text>
         <t>Denuncia por apremios ilegales
-Registrar si la institución realizó denuncia por apremios ilegales en el proceso de detención por parte de las fuerzas de seguridad, siempre que el niño, niña o adolescente lo haya manifestado o el equipo técnico lo haya detectado (Ley 26.061 Ley de protección integral de niños, niñas y adolescente: "El deber de informar"/Decreto 41/99 Código de ética de la función pública Art. 31 Obligación de denunciar/Códigos penales procesales de cada jurisdicción). Seleccionar Sí o No en el desplegable.
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "¿Presenta alguna discapacidad?".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: No, Sin datos, Sí.
+Registrar si la institución realizó denuncia por apremios ilegales en el proceso de detención por parte de las fuerzas de seguridad, siempre que el niño, niña o adolescente lo haya manifestado o el equipo técnico lo haya detectado (Ley 26.061 Ley de protección integral de niños, niñas y adolescente: "El deber de informar"/Decreto 41/99 Código de ética de la función pública Art. 31 Obligación de denunciar/Códigos penales procesales de cada jurisdicción). Seleccionar Sí o No en el desplegable.</t>
       </text>
     </comment>
     <comment ref="AO3" authorId="0" shapeId="0">
       <text>
         <t>Dependencia judicial
-Qué se espera: texto
-Máximo 255 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 255 caracteres.</t>
       </text>
     </comment>
     <comment ref="AP3" authorId="0" shapeId="0">
       <text>
         <t>Edad al ingreso
-Consignar la edad del adolescente a la fecha del ingreso al dispositivo.
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.
+Aviso: Entre 0 y 17.
+Aviso: No puede ser posterior a hoy.
+Consignar la edad del adolescente a la fecha del ingreso al dispositivo.</t>
       </text>
     </comment>
     <comment ref="AQ3" authorId="0" shapeId="0">
       <text>
         <t>Observaciones
-Qué se espera: texto
-No es obligatorio.</t>
+Opcional
+Qué va: Texto.</t>
       </text>
     </comment>
   </commentList>
@@ -1283,7 +1265,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Niño o adolescente</t>
+          <t>Niño, niña o adolescente</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
@@ -1325,7 +1307,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>ID del Niño, niña o Adolescente *</t>
+          <t>ID del niño, niña o adolescente *</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -3293,61 +3275,61 @@
   </mergeCells>
   <dataValidations count="19">
     <dataValidation sqref="B4:B203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Provincia&quot;." promptTitle="Provincia" prompt="Identificar la provincia o jurisdicción correspondiente" type="list">
-      <formula1>LISTAS!$M$2:$M$25</formula1>
+      <formula1>Listas!$M$2:$M$25</formula1>
     </dataValidation>
     <dataValidation sqref="D4:D203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Tipo de dispositivo&quot;." promptTitle="Tipo de dispositivo" prompt="Seleccionar el tipo de dispositivo correspondiente de la lista desplegable: Medida Penal en Territorio, Establecimiento de Restricción de Libertad, Establecimiento de Privación de Libertad o Prisión Domiciliaria." type="list">
-      <formula1>LISTAS!$R$2:$R$5</formula1>
+      <formula1>Listas!$R$2:$R$5</formula1>
     </dataValidation>
     <dataValidation sqref="J4:J203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Situación de documentación&quot;." promptTitle="Situación de documentación" prompt="Consignar la situación de cada adolescente en relación a la documentación de acuerdo a las siguientes categorías que se encuentran en la lista desplegable: Posee N° DNI, No posee N° DNI, DNI en trámite, Posee N° documento extranjero o Sin datos. Cabe dest" type="list">
-      <formula1>LISTAS!$N$2:$N$8</formula1>
+      <formula1>Listas!$N$2:$N$8</formula1>
     </dataValidation>
     <dataValidation sqref="L4:L203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Género&quot;." promptTitle="Género" prompt="Utilizar las categorías: Maculino, Femenino, Otros, Sin datos que se encuentran en la lista desplegable." type="list">
-      <formula1>LISTAS!$F$2:$F$5</formula1>
+      <formula1>Listas!$F$2:$F$5</formula1>
     </dataValidation>
     <dataValidation sqref="M4:M203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;País de nacimiento&quot;." promptTitle="País de nacimiento" prompt="Indicar el país de origen de cada adolescente según el desplegable incluido." type="list">
-      <formula1>LISTAS!$I$2:$I$247</formula1>
+      <formula1>Listas!$I$2:$I$247</formula1>
     </dataValidation>
     <dataValidation sqref="P4:P203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;¿Asiste a institución educativa?&quot;." promptTitle="¿Asiste a institución educativa?" prompt="Seleccionar de la lista desplegable." type="list">
-      <formula1>LISTAS!$B$2:$B$5</formula1>
+      <formula1>Listas!$B$2:$B$5</formula1>
     </dataValidation>
     <dataValidation sqref="Q4:Q203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Máximo nivel educativo alcanzado&quot;." promptTitle="Máximo nivel educativo alcanzado" prompt="Seleccionar en el menú desplegable, el nivel educativo alcanzado a la fecha del relevamiento." type="list">
-      <formula1>LISTAS!$G$2:$G$13</formula1>
+      <formula1>Listas!$G$2:$G$13</formula1>
     </dataValidation>
     <dataValidation sqref="R4:R203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Enfermedad crónica&quot;." promptTitle="Enfermedad crónica" prompt="Indicar si el adolescente presenta alguna enfermedad crónica." type="list">
-      <formula1>LISTAS!$K$2:$K$4</formula1>
+      <formula1>Listas!$K$2:$K$4</formula1>
     </dataValidation>
     <dataValidation sqref="S4:S203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Consumo problemático de sustancias&quot;." promptTitle="Consumo problemático de sustanci" prompt="Indicar si el adolescente presenta consumo problemático de sustancias." type="list">
-      <formula1>LISTAS!$K$2:$K$4</formula1>
+      <formula1>Listas!$K$2:$K$4</formula1>
     </dataValidation>
     <dataValidation sqref="T4:T203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;¿Presenta alguna discapacidad?&quot;." promptTitle="¿Presenta alguna discapacidad?" prompt="Indicar si el adolescente presenta alguna discapacidad. En caso de responder positivamente, en la columna siguiente deberá especificar el tipo de discapacidad." type="list">
-      <formula1>LISTAS!$K$2:$K$4</formula1>
+      <formula1>Listas!$K$2:$K$4</formula1>
     </dataValidation>
     <dataValidation sqref="U4:U203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Tipo de discapacidad&quot;." promptTitle="Tipo de discapacidad" prompt="Seleccionar el tipo de discapacidad según las opciones proporcionadas en el desplegable: visual, auditiva, mental, visceral, motora, otros (especificar en observaciones), sin datos." type="list">
-      <formula1>LISTAS!$Q$2:$Q$8</formula1>
+      <formula1>Listas!$Q$2:$Q$8</formula1>
     </dataValidation>
     <dataValidation sqref="V4:V203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;¿Posee CUD?&quot;." promptTitle="¿Posee CUD?" prompt="Responder según opciones del desplegable: Sí, No, En trámite, Sin datos. El Certificado Único de Discapacidad (CUD) es un documento que certifica la discapacidad de la persona y le permite acceder a derechos y prestaciones que brinda el Estado. El CUD es " type="list">
-      <formula1>LISTAS!$J$2:$J$5</formula1>
+      <formula1>Listas!$J$2:$J$5</formula1>
     </dataValidation>
     <dataValidation sqref="W4:W203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cobertura salud&quot;." promptTitle="Cobertura salud" prompt="Responder según opciones del desplegable: PAMI, IOMA, Obra social provincial, Obra social privada, Prepaga, Sin cobertura, Sin datos" type="list">
-      <formula1>LISTAS!$C$2:$C$8</formula1>
+      <formula1>Listas!$C$2:$C$8</formula1>
     </dataValidation>
     <dataValidation sqref="X4:X203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;¿Se identifica con algún pueblo originario?&quot;." promptTitle="¿Se identifica con algún pueblo " prompt="Consignar si el joven pertenece a un pueblo originario, utilizando las categorías Sí, No o Sin datos del desplegable. En caso de que la respuesta sea Sí , deberá especificarse en la columna siguiente el pueblo originario con el cual el adolescente se iden" type="list">
-      <formula1>LISTAS!$K$2:$K$4</formula1>
+      <formula1>Listas!$K$2:$K$4</formula1>
     </dataValidation>
     <dataValidation sqref="Z4:Z203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Asignación Universal por Hijo&quot;." promptTitle="Asignación Universal por Hijo" prompt="Indicar si el joven percibe o no la Asignación Universal por Hijo de acuerdo a los ítems de respuesta desplegables. Debe tenerse en cuenta que aunque el/la adolescente sea titular de la percepción del beneficio no implica que sea la persona que recibe el " type="list">
-      <formula1>LISTAS!$A$2:$A$5</formula1>
+      <formula1>Listas!$A$2:$A$5</formula1>
     </dataValidation>
     <dataValidation sqref="AA4:AA203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;¿Tiene hijos/as?&quot;." promptTitle="¿Tiene hijos/as?" prompt="Completarse por Sí, No o Sin datos. Es indistinto si los/as hijos/as se encuentran en el dispositivo junto a sus progenitores/as." type="list">
-      <formula1>LISTAS!$K$2:$K$4</formula1>
+      <formula1>Listas!$K$2:$K$4</formula1>
     </dataValidation>
     <dataValidation sqref="AD4:AD203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Procedencia inmediata&quot;." promptTitle="Procedencia inmediata" prompt="Consignar la procedencia inmediatamente anterior al ingreso al dispositivo, de acuerdo con las siguientes opciones: Policía provincial, Gendarmería, Prefectura, Infantería, CAD, Comisaría, Juzgado (sin intervención de otro dispositivo penal juvenil), Esta" type="list">
-      <formula1>LISTAS!$L$2:$L$14</formula1>
+      <formula1>Listas!$L$2:$L$14</formula1>
     </dataValidation>
     <dataValidation sqref="AG4:AG203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Situación procesal&quot;." promptTitle="Situación procesal" prompt="Consignar la situación procesal de el/la adolescente utilizando las categorías del desplegable: Investigación penal, Elevación a juicio, Declaración de responsabilidad, Ejecución penal, Sentencia a revisión, Otros, Sin datos. En caso de encontrarse en eta" type="list">
-      <formula1>LISTAS!$O$2:$O$8</formula1>
+      <formula1>Listas!$O$2:$O$8</formula1>
     </dataValidation>
     <dataValidation sqref="AJ4:AJ203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Destino al egreso&quot;." promptTitle="Destino al egreso" prompt="Responder utilizando las categorías del desplegable." type="list">
-      <formula1>LISTAS!$D$2:$D$11</formula1>
+      <formula1>Listas!$D$2:$D$11</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3424,7 +3406,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Niño o adolescente</t>
+          <t>Niño, niña o adolescente</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -3466,7 +3448,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>ID del Niño, niña o Adolescente *</t>
+          <t>ID del niño, niña o adolescente *</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -5859,67 +5841,67 @@
   </mergeCells>
   <dataValidations count="21">
     <dataValidation sqref="B4:B203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Provincia&quot;." promptTitle="Provincia" prompt="Identificar la provincia o jurisdicción correspondiente" type="list">
-      <formula1>LISTAS!$M$2:$M$25</formula1>
+      <formula1>Listas!$M$2:$M$25</formula1>
     </dataValidation>
     <dataValidation sqref="D4:D203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Tipo de dispositivo&quot;." promptTitle="Tipo de dispositivo" prompt="Seleccionar el tipo de dispositivo correspondiente de la lista desplegable: Medida Penal en Territorio, Establecimiento de Restricción de Libertad, Establecimiento de Privación de Libertad o Prisión Domiciliaria." type="list">
-      <formula1>LISTAS!$S$2:$S$3</formula1>
+      <formula1>Listas!$S$2:$S$3</formula1>
     </dataValidation>
     <dataValidation sqref="J4:J203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Situación de documentación&quot;." type="list">
-      <formula1>LISTAS!$N$2:$N$8</formula1>
+      <formula1>Listas!$N$2:$N$8</formula1>
     </dataValidation>
     <dataValidation sqref="L4:L203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Género&quot;." type="list">
-      <formula1>LISTAS!$F$2:$F$5</formula1>
+      <formula1>Listas!$F$2:$F$5</formula1>
     </dataValidation>
     <dataValidation sqref="M4:M203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;País de nacimiento&quot;." type="list">
-      <formula1>LISTAS!$I$2:$I$247</formula1>
+      <formula1>Listas!$I$2:$I$247</formula1>
     </dataValidation>
     <dataValidation sqref="P4:P203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;¿Asiste a institución educativa?&quot;." type="list">
-      <formula1>LISTAS!$B$2:$B$5</formula1>
+      <formula1>Listas!$B$2:$B$5</formula1>
     </dataValidation>
     <dataValidation sqref="Q4:Q203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Máximo nivel educativo alcanzado&quot;." type="list">
-      <formula1>LISTAS!$G$2:$G$13</formula1>
+      <formula1>Listas!$G$2:$G$13</formula1>
     </dataValidation>
     <dataValidation sqref="R4:R203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Enfermedad crónica&quot;." type="list">
-      <formula1>LISTAS!$K$2:$K$4</formula1>
+      <formula1>Listas!$K$2:$K$4</formula1>
     </dataValidation>
     <dataValidation sqref="S4:S203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Consumo problemático de sustancias&quot;." type="list">
-      <formula1>LISTAS!$K$2:$K$4</formula1>
+      <formula1>Listas!$K$2:$K$4</formula1>
     </dataValidation>
     <dataValidation sqref="T4:T203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;¿Presenta alguna discapacidad?&quot;." type="list">
-      <formula1>LISTAS!$K$2:$K$4</formula1>
+      <formula1>Listas!$K$2:$K$4</formula1>
     </dataValidation>
     <dataValidation sqref="U4:U203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Tipo de discapacidad&quot;." type="list">
-      <formula1>LISTAS!$Q$2:$Q$8</formula1>
+      <formula1>Listas!$Q$2:$Q$8</formula1>
     </dataValidation>
     <dataValidation sqref="V4:V203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;¿Posee CUD?&quot;." type="list">
-      <formula1>LISTAS!$J$2:$J$5</formula1>
+      <formula1>Listas!$J$2:$J$5</formula1>
     </dataValidation>
     <dataValidation sqref="W4:W203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cobertura salud&quot;." type="list">
-      <formula1>LISTAS!$C$2:$C$8</formula1>
+      <formula1>Listas!$C$2:$C$8</formula1>
     </dataValidation>
     <dataValidation sqref="X4:X203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;¿Se identifica con algún pueblo originario?&quot;." type="list">
-      <formula1>LISTAS!$K$2:$K$4</formula1>
+      <formula1>Listas!$K$2:$K$4</formula1>
     </dataValidation>
     <dataValidation sqref="Z4:Z203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;¿Tiene hijos/as?&quot;." type="list">
-      <formula1>LISTAS!$K$2:$K$4</formula1>
+      <formula1>Listas!$K$2:$K$4</formula1>
     </dataValidation>
     <dataValidation sqref="AA4:AA203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Motivo de la aprehensión&quot;." type="list">
-      <formula1>LISTAS!$H$2:$H$8</formula1>
+      <formula1>Listas!$H$2:$H$8</formula1>
     </dataValidation>
     <dataValidation sqref="AE4:AE203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Fuerza de seguridad&quot;." promptTitle="Fuerza de seguridad" prompt="Identificar la fuerza de seguridad que ha efectuado la aprehensión de acuerdo con las opciones que aparecen en el desplegable: Policía Municipal, Policía Provincial, Policía Federal, Gendarmería, Prefectura, Infantería, Otros, Sin datos." type="list">
-      <formula1>LISTAS!$E$2:$E$9</formula1>
+      <formula1>Listas!$E$2:$E$9</formula1>
     </dataValidation>
     <dataValidation sqref="AH4:AH203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;¿Pasó por comisaría previo ingreso?&quot;." promptTitle="¿Pasó por comisaría previo ingre" prompt="Consignar si el adolescente pasó o no por una comisaría (tanto por trámites policiales y/o permanencia) previamente a su ingreso al establecimiento especializado de aprehensión según desplegable." type="list">
-      <formula1>LISTAS!$K$2:$K$4</formula1>
+      <formula1>Listas!$K$2:$K$4</formula1>
     </dataValidation>
     <dataValidation sqref="AI4:AI203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Tiempo en comisaría&quot;." promptTitle="Tiempo en comisaría" prompt="Especificar el tiempo de permanencia en la comisaría, de acuerdo con las opciones que ofrece el listado desplegable: Hasta 12 hs., Entre 12 y 24 hs., etc. Seleccionar del listado desplegable. En caso que el NNyA no haya pasado previamente por una dependen" type="list">
-      <formula1>LISTAS!$P$2:$P$13</formula1>
+      <formula1>Listas!$P$2:$P$13</formula1>
     </dataValidation>
     <dataValidation sqref="AL4:AL203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Destino al egreso&quot;." type="list">
-      <formula1>LISTAS!$D$2:$D$11</formula1>
+      <formula1>Listas!$D$2:$D$11</formula1>
     </dataValidation>
     <dataValidation sqref="AN4:AN203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Denuncia por apremios ilegales&quot;." promptTitle="Denuncia por apremios ilegales" prompt="Registrar si la institución realizó denuncia por apremios ilegales en el proceso de detención por parte de las fuerzas de seguridad, siempre que el niño, niña o adolescente lo haya manifestado o el equipo técnico lo haya detectado (Ley 26.061 Ley de prote" type="list">
-      <formula1>LISTAS!$K$2:$K$4</formula1>
+      <formula1>Listas!$K$2:$K$4</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5928,1075 +5910,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B91"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="95" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>Campo</t>
-        </is>
-      </c>
-      <c r="B1" s="9" t="inlineStr">
-        <is>
-          <t>Indicación para el llenado</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>Hoja: MPJ</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Fecha del relevamiento</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>Campo obligatorio.
-Formato de fecha: dd/mm/aaaa.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>Dispositivo</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Provincia</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>Identificar la provincia o jurisdicción correspondiente
-Debe elegirse un valor de la lista "Provincias".</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Nombre del dispositivo</t>
-        </is>
-      </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>Consignar el nombre completo del dispositivo (Establecimiento o Programa) en el cual se encuentran los jóvenes incluidos en el presente listado.
-Campo obligatorio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Tipo de dispositivo</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>Seleccionar el tipo de dispositivo correspondiente de la lista desplegable: Medida Penal en Territorio, Establecimiento de Restricción de Libertad, Establecimiento de Privación de Libertad o Prisión Domiciliaria.
-Debe elegirse un valor de la lista "Tipo de dispositivo".</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Dependencia institucional</t>
-        </is>
-      </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>Indicar el organismo del cual depende el dispositivo con el siguiente orden: Ministerio, Secretaría, Dirección (según corresponda).</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Localidad</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>Consignar localidad en la cual se encuentra ubicado el dispositivo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>Niño o adolescente</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>ID del Niño, niña o Adolescente</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>Identificador alfanumérico nominal único provincial asignado al NyA para seguimiento resguardando su identidad. En caso de existir.
-Campo obligatorio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Apellido/s</t>
-        </is>
-      </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>Consignar el/los apellido/s del adolescente, tal como figura/n en su documentación.
-Campo obligatorio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Nombre/s</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>Consignar el/los nombre/s del adolescente, tal como figura/n en su documentación.
-Campo obligatorio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Situación de documentación</t>
-        </is>
-      </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>Consignar la situación de cada adolescente en relación a la documentación de acuerdo a las siguientes categorías que se encuentran en la lista desplegable: Posee N° DNI, No posee N° DNI, DNI en trámite, Posee N° documento extranjero o Sin datos. Cabe destacar que las opciones Posee N° DNI y No posee N° DNI hacen referencia al hecho de que se haya realizado o no el trámite para la obtención del Documento Nacional de Identidad. En este sentido, es importante mencionar que la indagación aquí realizada no permite identificar otro tipo de situaciones problemáticas vinculadas con la documentación, tales como la falta de renovación, o casos de extravío o deterioro de los mismos, entre otras.
-Debe elegirse un valor de la lista "Situación de documentación".</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Nº DNI</t>
-        </is>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>Informar el número de DNI del adolescente, sin puntos ni espacios.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Género</t>
-        </is>
-      </c>
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>Utilizar las categorías: Maculino, Femenino, Otros, Sin datos que se encuentran en la lista desplegable.
-Debe elegirse un valor de la lista "Género".</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>País de nacimiento</t>
-        </is>
-      </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>Indicar el país de origen de cada adolescente según el desplegable incluido.
-Debe elegirse un valor de la lista "País de nacimiento".</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Fecha de nacimiento</t>
-        </is>
-      </c>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>Especificar la fecha de nacimiento del adolescente utilizando el siguiente formato: DD/MM/AAAA. Por ejemplo: 01/03/2001.
-Campo obligatorio.
-Formato de fecha: dd/mm/aaaa.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Edad</t>
-        </is>
-      </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>Consignar la edad del adolescente a la fecha del presente relevamiento.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>¿Asiste a institución educativa?</t>
-        </is>
-      </c>
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t>Seleccionar de la lista desplegable.
-Debe elegirse un valor de la lista "¿Asiste a institución educativa?".</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Máximo nivel educativo alcanzado</t>
-        </is>
-      </c>
-      <c r="B21" s="11" t="inlineStr">
-        <is>
-          <t>Seleccionar en el menú desplegable, el nivel educativo alcanzado a la fecha del relevamiento.
-Debe elegirse un valor de la lista "Máximo nivel educativo alcanzado".</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Enfermedad crónica</t>
-        </is>
-      </c>
-      <c r="B22" s="11" t="inlineStr">
-        <is>
-          <t>Indicar si el adolescente presenta alguna enfermedad crónica.
-Debe elegirse un valor de la lista "¿Presenta alguna discapacidad?".</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Consumo problemático de sustancias</t>
-        </is>
-      </c>
-      <c r="B23" s="11" t="inlineStr">
-        <is>
-          <t>Indicar si el adolescente presenta consumo problemático de sustancias.
-Debe elegirse un valor de la lista "¿Presenta alguna discapacidad?".</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>¿Presenta alguna discapacidad?</t>
-        </is>
-      </c>
-      <c r="B24" s="11" t="inlineStr">
-        <is>
-          <t>Indicar si el adolescente presenta alguna discapacidad. En caso de responder positivamente, en la columna siguiente deberá especificar el tipo de discapacidad.
-Debe elegirse un valor de la lista "¿Presenta alguna discapacidad?".</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Tipo de discapacidad</t>
-        </is>
-      </c>
-      <c r="B25" s="11" t="inlineStr">
-        <is>
-          <t>Seleccionar el tipo de discapacidad según las opciones proporcionadas en el desplegable: visual, auditiva, mental, visceral, motora, otros (especificar en observaciones), sin datos.
-Debe elegirse un valor de la lista "Tipo de discapacidad".</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>¿Posee CUD?</t>
-        </is>
-      </c>
-      <c r="B26" s="11" t="inlineStr">
-        <is>
-          <t>Responder según opciones del desplegable: Sí, No, En trámite, Sin datos. El Certificado Único de Discapacidad (CUD) es un documento que certifica la discapacidad de la persona y le permite acceder a derechos y prestaciones que brinda el Estado. El CUD es un documento público válido en todo el país que permite ejercer los derechos y acceder a las prestaciones previstas en las leyes nacionales 22.431 y 24.901.
-Debe elegirse un valor de la lista "¿Posee CUD?".</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Cobertura salud</t>
-        </is>
-      </c>
-      <c r="B27" s="11" t="inlineStr">
-        <is>
-          <t>Responder según opciones del desplegable: PAMI, IOMA, Obra social provincial, Obra social privada, Prepaga, Sin cobertura, Sin datos
-Debe elegirse un valor de la lista "Cobertura salud".</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>¿Se identifica con algún pueblo originario?</t>
-        </is>
-      </c>
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>Consignar si el joven pertenece a un pueblo originario, utilizando las categorías Sí, No o Sin datos del desplegable. En caso de que la respuesta sea Sí , deberá especificarse en la columna siguiente el pueblo originario con el cual el adolescente se identifica, en caso de que la respuesta sea No, consignar en la columna siguiente No corresponde.
-Debe elegirse un valor de la lista "¿Presenta alguna discapacidad?".</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Pueblo originario (especificar)</t>
-        </is>
-      </c>
-      <c r="B29" s="11" t="inlineStr">
-        <is>
-          <t>Pregunta abierta.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Asignación Universal por Hijo</t>
-        </is>
-      </c>
-      <c r="B30" s="11" t="inlineStr">
-        <is>
-          <t>Indicar si el joven percibe o no la Asignación Universal por Hijo de acuerdo a los ítems de respuesta desplegables. Debe tenerse en cuenta que aunque el/la adolescente sea titular de la percepción del beneficio no implica que sea la persona que recibe el dinero de la asignación. La percepción refiere sólo a la titularidad.
-Debe elegirse un valor de la lista "Asignación Universal por Hijo".</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>¿Tiene hijos/as?</t>
-        </is>
-      </c>
-      <c r="B31" s="11" t="inlineStr">
-        <is>
-          <t>Completarse por Sí, No o Sin datos. Es indistinto si los/as hijos/as se encuentran en el dispositivo junto a sus progenitores/as.
-Debe elegirse un valor de la lista "¿Presenta alguna discapacidad?".</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="12" t="inlineStr">
-        <is>
-          <t>Datos penales / Medida</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Descripción causa penal/contravención</t>
-        </is>
-      </c>
-      <c r="B33" s="11" t="inlineStr">
-        <is>
-          <t>Identificar la causa penal o contravención por la cual el/la adolescente se encuentra en el dispositivo. En caso de que exista más de una causa, por favor consignar todas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Fecha de ingreso al dispositivo</t>
-        </is>
-      </c>
-      <c r="B34" s="11" t="inlineStr">
-        <is>
-          <t>Especificar el día de ingreso del adolescente al dispositivo utilizando el siguiente formato DD/MD/AAAA. Ej.: 01/02/2021
-Formato de fecha: dd/mm/aaaa.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Procedencia inmediata</t>
-        </is>
-      </c>
-      <c r="B35" s="11" t="inlineStr">
-        <is>
-          <t>Consignar la procedencia inmediatamente anterior al ingreso al dispositivo, de acuerdo con las siguientes opciones: Policía provincial, Gendarmería, Prefectura, Infantería, CAD, Comisaría, Juzgado (sin intervención de otro dispositivo penal juvenil), Establecimiento de privación de libertad, Establecimiento de restricción de libertad, Medida penal en territorio, Defensoría de menores, Otros o Sin datos.
-Debe elegirse un valor de la lista "Procedencia inmediata".</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Especificar procedencia</t>
-        </is>
-      </c>
-      <c r="B36" s="11" t="inlineStr">
-        <is>
-          <t>En caso de ser derivado por una comisaría, especificar el número de comisaría. Si se trata de un CAD, Establecimiento de privación de libertad, Establecimiento de restricción de libertad, Medida penal en territorio, indicar el nombre del dispositivo y localización geográfica.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Dependencia judicial</t>
-        </is>
-      </c>
-      <c r="B37" s="11" t="inlineStr">
-        <is>
-          <t>Consignar la dependencia Judicial.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Situación procesal</t>
-        </is>
-      </c>
-      <c r="B38" s="11" t="inlineStr">
-        <is>
-          <t>Consignar la situación procesal de el/la adolescente utilizando las categorías del desplegable: Investigación penal, Elevación a juicio, Declaración de responsabilidad, Ejecución penal, Sentencia a revisión, Otros, Sin datos. En caso de encontrarse en etapa de Ejecución Penal, especificar el monto de la pena en la columna siguiente.
-Debe elegirse un valor de la lista "Situación procesal".</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Monto de la pena</t>
-        </is>
-      </c>
-      <c r="B39" s="11" t="inlineStr">
-        <is>
-          <t>Pregunta abierta. Entrada numérica según cada caso individual.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Fecha de egreso del dispositivo</t>
-        </is>
-      </c>
-      <c r="B40" s="11" t="inlineStr">
-        <is>
-          <t>Especificar el día de egreso del adolescente al dispositivo utilizando el siguiente formato DD/MD/AAAA. Ej.: 01/02/2021
-Formato de fecha: dd/mm/aaaa.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Destino al egreso</t>
-        </is>
-      </c>
-      <c r="B41" s="11" t="inlineStr">
-        <is>
-          <t>Responder utilizando las categorías del desplegable.
-Debe elegirse un valor de la lista "Destino al egreso".</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Especificar destino al egreso</t>
-        </is>
-      </c>
-      <c r="B42" s="11" t="inlineStr">
-        <is>
-          <t>En caso de que en la columna anterior se haya elegido egreso a un dispositivo penal, consignar el nombre del mismo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Observaciones</t>
-        </is>
-      </c>
-      <c r="B43" s="11" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="10" t="inlineStr">
-        <is>
-          <t>Hoja: DAE</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Fecha del relevamiento</t>
-        </is>
-      </c>
-      <c r="B46" s="11" t="inlineStr">
-        <is>
-          <t>Campo obligatorio.
-Formato de fecha: dd/mm/aaaa.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="12" t="inlineStr">
-        <is>
-          <t>Dispositivo/espacio</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Provincia</t>
-        </is>
-      </c>
-      <c r="B48" s="11" t="inlineStr">
-        <is>
-          <t>Identificar la provincia o jurisdicción correspondiente
-Debe elegirse un valor de la lista "Provincias".</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Nombre del dispositivo</t>
-        </is>
-      </c>
-      <c r="B49" s="11" t="inlineStr">
-        <is>
-          <t>Consignar el nombre completo del dispositivo (Establecimiento o Programa) en el cual se encuentran los jóvenes incluidos en el presente listado.
-Campo obligatorio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Tipo de dispositivo</t>
-        </is>
-      </c>
-      <c r="B50" s="11" t="inlineStr">
-        <is>
-          <t>Seleccionar el tipo de dispositivo correspondiente de la lista desplegable: Medida Penal en Territorio, Establecimiento de Restricción de Libertad, Establecimiento de Privación de Libertad o Prisión Domiciliaria.
-Debe elegirse un valor de la lista "Tipo de dispositivo".</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Dependencia institucional</t>
-        </is>
-      </c>
-      <c r="B51" s="11" t="inlineStr">
-        <is>
-          <t>Indicar el organismo del cual depende el dispositivo con el siguiente orden: Ministerio, Secretaría, Dirección (según corresponda).</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Localidad</t>
-        </is>
-      </c>
-      <c r="B52" s="11" t="inlineStr">
-        <is>
-          <t>Consignar localidad en la cual se encuentra ubicado el dispositivo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="12" t="inlineStr">
-        <is>
-          <t>Niño o adolescente</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>ID del Niño, niña o Adolescente</t>
-        </is>
-      </c>
-      <c r="B54" s="11" t="inlineStr">
-        <is>
-          <t>Campo obligatorio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Apellido/s</t>
-        </is>
-      </c>
-      <c r="B55" s="11" t="inlineStr">
-        <is>
-          <t>Campo obligatorio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Nombre/s</t>
-        </is>
-      </c>
-      <c r="B56" s="11" t="inlineStr">
-        <is>
-          <t>Campo obligatorio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Situación de documentación</t>
-        </is>
-      </c>
-      <c r="B57" s="11" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Situación de documentación".</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Nº DNI</t>
-        </is>
-      </c>
-      <c r="B58" s="11" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Género</t>
-        </is>
-      </c>
-      <c r="B59" s="11" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Género".</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>País de nacimiento</t>
-        </is>
-      </c>
-      <c r="B60" s="11" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "País de nacimiento".</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Fecha de nacimiento</t>
-        </is>
-      </c>
-      <c r="B61" s="11" t="inlineStr">
-        <is>
-          <t>Campo obligatorio.
-Formato de fecha: dd/mm/aaaa.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Edad</t>
-        </is>
-      </c>
-      <c r="B62" s="11" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>¿Asiste a institución educativa?</t>
-        </is>
-      </c>
-      <c r="B63" s="11" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "¿Asiste a institución educativa?".</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Máximo nivel educativo alcanzado</t>
-        </is>
-      </c>
-      <c r="B64" s="11" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Máximo nivel educativo alcanzado".</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Enfermedad crónica</t>
-        </is>
-      </c>
-      <c r="B65" s="11" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "¿Presenta alguna discapacidad?".</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Consumo problemático de sustancias</t>
-        </is>
-      </c>
-      <c r="B66" s="11" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "¿Presenta alguna discapacidad?".</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>¿Presenta alguna discapacidad?</t>
-        </is>
-      </c>
-      <c r="B67" s="11" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "¿Presenta alguna discapacidad?".</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Tipo de discapacidad</t>
-        </is>
-      </c>
-      <c r="B68" s="11" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Tipo de discapacidad".</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>¿Posee CUD?</t>
-        </is>
-      </c>
-      <c r="B69" s="11" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "¿Posee CUD?".</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Cobertura salud</t>
-        </is>
-      </c>
-      <c r="B70" s="11" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Cobertura salud".</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>¿Se identifica con algún pueblo originario?</t>
-        </is>
-      </c>
-      <c r="B71" s="11" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "¿Presenta alguna discapacidad?".</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Pueblo originario (especificar)</t>
-        </is>
-      </c>
-      <c r="B72" s="11" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>¿Tiene hijos/as?</t>
-        </is>
-      </c>
-      <c r="B73" s="11" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "¿Presenta alguna discapacidad?".</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="12" t="inlineStr">
-        <is>
-          <t>Datos penales / Medida</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Motivo de la aprehensión</t>
-        </is>
-      </c>
-      <c r="B75" s="11" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Motivo de la aprehensión".</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Descripción causa/contravención</t>
-        </is>
-      </c>
-      <c r="B76" s="11" t="inlineStr">
-        <is>
-          <t>Identificar la causa penal o contravención por la cual el/la adolescente se encuentra en el dispositivo. En caso de que exista más de una causa, por favor consignar todas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Fecha de ingreso al dispositivo</t>
-        </is>
-      </c>
-      <c r="B77" s="11" t="inlineStr">
-        <is>
-          <t>Formato de fecha: dd/mm/aaaa.</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Hora de ingreso al dispositivo</t>
-        </is>
-      </c>
-      <c r="B78" s="11" t="inlineStr">
-        <is>
-          <t>Consignar la hora de ingreso al establecimiento utilizando el siguiente formato HH:MM, en formato 24 hs. Ej.: 22:30. Recuerde utilizar los dos puntos para separar hora de minutos.
-Formato de hora: hh:mm.</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Fuerza de seguridad</t>
-        </is>
-      </c>
-      <c r="B79" s="11" t="inlineStr">
-        <is>
-          <t>Identificar la fuerza de seguridad que ha efectuado la aprehensión de acuerdo con las opciones que aparecen en el desplegable: Policía Municipal, Policía Provincial, Policía Federal, Gendarmería, Prefectura, Infantería, Otros, Sin datos.
-Debe elegirse un valor de la lista "Fuerza de seguridad".</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>N° comisaría o dependencia</t>
-        </is>
-      </c>
-      <c r="B80" s="11" t="inlineStr">
-        <is>
-          <t>Detallar la dependencia a la que pertenece la fuerza que ha efectuado la aprehensión, de acuerdo con las siguientes opciones: Comisaría N° XX, Alcaldía N° XX, u otro/s.</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Departamento de la dependencia</t>
-        </is>
-      </c>
-      <c r="B81" s="11" t="inlineStr">
-        <is>
-          <t>Especificar el departamento en el cual se ubica la dependencia policial de procedencia que efectuó la aprehensión.</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>¿Pasó por comisaría previo ingreso?</t>
-        </is>
-      </c>
-      <c r="B82" s="11" t="inlineStr">
-        <is>
-          <t>Consignar si el adolescente pasó o no por una comisaría (tanto por trámites policiales y/o permanencia) previamente a su ingreso al establecimiento especializado de aprehensión según desplegable.
-Debe elegirse un valor de la lista "¿Presenta alguna discapacidad?".</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Tiempo en comisaría</t>
-        </is>
-      </c>
-      <c r="B83" s="11" t="inlineStr">
-        <is>
-          <t>Especificar el tiempo de permanencia en la comisaría, de acuerdo con las opciones que ofrece el listado desplegable: Hasta 12 hs., Entre 12 y 24 hs., etc. Seleccionar del listado desplegable. En caso que el NNyA no haya pasado previamente por una dependencia policial, seleccionar No corresponde.
-Debe elegirse un valor de la lista "Tiempo en comisaría".</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Fecha de egreso del dispositivo</t>
-        </is>
-      </c>
-      <c r="B84" s="11" t="inlineStr">
-        <is>
-          <t>Formato de fecha: dd/mm/aaaa.</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Hora de egreso del dispositivo</t>
-        </is>
-      </c>
-      <c r="B85" s="11" t="inlineStr">
-        <is>
-          <t>Consignar la hora de egreso del dispositivo utilizando el siguiente formato HH:MM, en formato 24 hs. Ej.: 22:30. Recuerde utilizar los dos puntos para separar hora de minutos.
-Formato de hora: hh:mm.</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Destino al egreso</t>
-        </is>
-      </c>
-      <c r="B86" s="11" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Destino al egreso".</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Especificar destino al egreso</t>
-        </is>
-      </c>
-      <c r="B87" s="11" t="n"/>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Denuncia por apremios ilegales</t>
-        </is>
-      </c>
-      <c r="B88" s="11" t="inlineStr">
-        <is>
-          <t>Registrar si la institución realizó denuncia por apremios ilegales en el proceso de detención por parte de las fuerzas de seguridad, siempre que el niño, niña o adolescente lo haya manifestado o el equipo técnico lo haya detectado (Ley 26.061 Ley de protección integral de niños, niñas y adolescente: "El deber de informar"/Decreto 41/99 Código de ética de la función pública Art. 31 Obligación de denunciar/Códigos penales procesales de cada jurisdicción). Seleccionar Sí o No en el desplegable.
-Debe elegirse un valor de la lista "¿Presenta alguna discapacidad?".</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Dependencia judicial</t>
-        </is>
-      </c>
-      <c r="B89" s="11" t="n"/>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Edad al ingreso</t>
-        </is>
-      </c>
-      <c r="B90" s="11" t="inlineStr">
-        <is>
-          <t>Consignar la edad del adolescente a la fecha del ingreso al dispositivo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Observaciones</t>
-        </is>
-      </c>
-      <c r="B91" s="11" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
